--- a/StructureDefinition-ct-pachymetry.xlsx
+++ b/StructureDefinition-ct-pachymetry.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ct-pachymetry.xlsx
+++ b/StructureDefinition-ct-pachymetry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2110,17 +2110,17 @@
   <dimension ref="A1:AP114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.6484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.09375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2129,28 +2129,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-ct-pachymetry.xlsx
+++ b/StructureDefinition-ct-pachymetry.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$115</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4431" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,6 +634,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:exam</t>
+  </si>
+  <si>
+    <t>exam</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -645,18 +670,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -676,6 +689,15 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="corneal-tomography-pachymetry"/&gt;
+    &lt;display value="Corneal tomography, pachymetry analysis"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -760,7 +782,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ophthalmic-encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1068,9 +1090,6 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -1080,7 +1099,7 @@
     <t>bodySiteEye</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>
@@ -1604,6 +1623,15 @@
     <t>CCT at apex - central corneal thickness at corneal apex</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="central-corneal-thickness"/&gt;
+    &lt;display value="Central corneal thickness"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.component:cctApex.value[x]</t>
   </si>
   <si>
@@ -1641,6 +1669,15 @@
     <t>CCT at pupil center - corneal thickness at pupil center, may differ from apex</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="corneal-thickness-pupil-centre"/&gt;
+    &lt;display value="Corneal thickness at pupil centre"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.component:cctPupil.value[x]</t>
   </si>
   <si>
@@ -1674,6 +1711,15 @@
     <t>Thinnest point value - thickness at thinnest corneal point, critical for keratoconus</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="corneal-thickness-thinnest"/&gt;
+    &lt;display value="Thinnest corneal thickness"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.component:thinnest.value[x]</t>
   </si>
   <si>
@@ -1707,6 +1753,15 @@
     <t>Thinnest point location (x,y) - location of thinnest point from center</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="corneal-thinnest-point-location"/&gt;
+    &lt;display value="Thinnest corneal point location"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.component:thinnestLoc.value[x]</t>
   </si>
   <si>
@@ -1740,6 +1795,15 @@
     <t>Corneal volume - total corneal volume</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="corneal-volume"/&gt;
+    &lt;display value="Corneal volume"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.component:cornealVol.value[x]</t>
   </si>
   <si>
@@ -1771,6 +1835,15 @@
   </si>
   <si>
     <t>Pachymetry progression index - rate of thickness change from thinnest point (BAD component Dp)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="pachymetric-progression"/&gt;
+    &lt;display value="Pachymetric progression index (BAD Dp)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:pachyProgression.value[x]</t>
@@ -2107,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP114"/>
+  <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.73828125" customWidth="true" bestFit="true"/>
@@ -3843,7 +3916,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>191</v>
       </c>
@@ -3893,7 +3966,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3911,25 +3984,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3956,10 +4027,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3967,14 +4038,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3990,22 +4063,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -4015,7 +4088,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4030,13 +4103,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4054,13 +4127,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -4069,34 +4142,34 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4115,19 +4188,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4137,7 +4210,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -4152,13 +4225,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4176,10 +4249,10 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -4191,30 +4264,30 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4222,13 +4295,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4237,18 +4310,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4296,13 +4371,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -4311,44 +4386,44 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4357,20 +4432,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4418,13 +4491,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -4433,19 +4506,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4453,14 +4526,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4479,19 +4552,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4540,7 +4613,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4555,34 +4628,34 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4592,7 +4665,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>83</v>
@@ -4601,18 +4674,20 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4660,7 +4735,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4675,19 +4750,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4695,10 +4770,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4709,7 +4784,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4721,18 +4796,18 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4780,13 +4855,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4795,19 +4870,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4815,10 +4890,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4829,7 +4904,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4841,19 +4916,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4902,45 +4975,45 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4960,22 +5033,22 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5000,13 +5073,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5024,7 +5097,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5033,7 +5106,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -5042,38 +5115,38 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -5088,16 +5161,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5122,40 +5195,40 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -5164,31 +5237,31 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5198,7 +5271,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
@@ -5207,19 +5280,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5244,13 +5317,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5268,7 +5341,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5286,27 +5359,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5317,7 +5390,7 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>95</v>
@@ -5329,18 +5402,20 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5364,13 +5439,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5388,13 +5463,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5406,27 +5481,27 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5440,7 +5515,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5449,15 +5524,17 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5482,13 +5559,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5506,7 +5583,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5518,44 +5595,44 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5567,17 +5644,15 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5614,73 +5689,71 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AF29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
@@ -5689,15 +5762,17 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>337</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>338</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5734,19 +5809,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5770,7 +5845,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5779,14 +5854,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5798,7 +5875,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
@@ -5807,13 +5884,13 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5864,19 +5941,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5888,7 +5965,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5899,10 +5976,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5913,7 +5990,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5925,13 +6002,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5970,43 +6047,43 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AD32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE32" t="s" s="2">
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6028,10 +6105,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -6043,7 +6120,7 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>348</v>
@@ -6051,16 +6128,14 @@
       <c r="M33" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -6090,31 +6165,31 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6126,7 +6201,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6137,10 +6212,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6163,22 +6238,24 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>355</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6220,10 +6297,10 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>94</v>
@@ -6232,7 +6309,7 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6255,10 +6332,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6266,10 +6343,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6278,23 +6355,19 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6342,13 +6415,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6363,10 +6436,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>367</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6377,10 +6450,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6391,7 +6464,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6403,19 +6476,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6464,13 +6537,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6485,10 +6558,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6499,10 +6572,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6522,22 +6595,22 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6562,13 +6635,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6586,7 +6659,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6607,10 +6680,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6621,10 +6694,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6647,18 +6720,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>386</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6682,13 +6757,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6706,7 +6781,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6724,27 +6799,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6758,7 +6833,7 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -6767,16 +6842,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6826,7 +6901,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6844,27 +6919,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6875,10 +6950,10 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
@@ -6887,20 +6962,18 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6948,45 +7021,45 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM40" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6997,7 +7070,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -7009,16 +7082,20 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -7066,19 +7143,19 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -7087,10 +7164,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7101,21 +7178,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -7127,17 +7204,15 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7186,19 +7261,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7210,7 +7285,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7221,14 +7296,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7241,26 +7316,24 @@
         <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7308,7 +7381,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7332,7 +7405,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7343,42 +7416,46 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7426,19 +7503,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7447,10 +7524,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>425</v>
+        <v>137</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7461,10 +7538,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7487,13 +7564,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7544,7 +7621,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7553,7 +7630,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7565,7 +7642,7 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>429</v>
@@ -7605,7 +7682,7 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>192</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>431</v>
@@ -7613,12 +7690,8 @@
       <c r="M46" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7642,13 +7715,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>435</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7675,7 +7748,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7684,13 +7757,13 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>303</v>
+        <v>433</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7701,10 +7774,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7715,7 +7788,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7730,16 +7803,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7764,13 +7837,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7788,13 +7861,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7806,13 +7879,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7823,10 +7896,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7837,7 +7910,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7849,17 +7922,19 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7884,13 +7959,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7908,13 +7983,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7926,13 +8001,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>451</v>
+        <v>308</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7943,10 +8018,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7969,16 +8044,18 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>324</v>
+        <v>451</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -8026,7 +8103,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8047,7 +8124,7 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>455</v>
@@ -8075,7 +8152,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -8084,20 +8161,18 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8152,7 +8227,7 @@
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -8167,10 +8242,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8181,10 +8256,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8207,16 +8282,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8266,7 +8341,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8287,10 +8362,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8301,10 +8376,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8312,7 +8387,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>82</v>
@@ -8327,20 +8402,18 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>404</v>
+        <v>468</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8376,17 +8449,19 @@
         <v>83</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8407,10 +8482,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8421,10 +8496,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8432,10 +8507,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8444,19 +8519,23 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8492,31 +8571,29 @@
         <v>83</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8525,10 +8602,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8539,21 +8616,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8565,17 +8642,15 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8624,19 +8699,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8648,7 +8723,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8659,14 +8734,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8679,26 +8754,24 @@
         <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8746,7 +8819,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8770,7 +8843,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8781,45 +8854,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8844,13 +8917,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8868,34 +8941,34 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8903,10 +8976,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8914,7 +8987,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>94</v>
@@ -8929,19 +9002,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>273</v>
+        <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8966,13 +9039,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8990,10 +9063,10 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>94</v>
@@ -9011,16 +9084,16 @@
         <v>488</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9048,22 +9121,22 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9088,13 +9161,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9121,7 +9194,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9130,19 +9203,19 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9154,14 +9227,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -9176,16 +9249,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9210,13 +9283,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9240,10 +9313,10 @@
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9252,31 +9325,31 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9295,19 +9368,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9332,13 +9405,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9356,7 +9429,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9374,64 +9447,62 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C61" t="s" s="2">
         <v>498</v>
       </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9480,7 +9551,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9501,10 +9572,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9513,44 +9584,50 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9598,19 +9675,19 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -9619,10 +9696,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9633,21 +9710,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9659,17 +9736,15 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9718,19 +9793,19 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -9742,7 +9817,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9753,14 +9828,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9773,26 +9848,24 @@
         <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9840,7 +9913,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9864,7 +9937,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9875,45 +9948,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>503</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9938,13 +10011,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9962,34 +10035,34 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9997,10 +10070,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10008,7 +10081,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>94</v>
@@ -10023,19 +10096,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>505</v>
+        <v>192</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10045,7 +10118,7 @@
         <v>83</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>83</v>
@@ -10060,13 +10133,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10084,10 +10157,10 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>94</v>
@@ -10105,21 +10178,21 @@
         <v>488</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>489</v>
@@ -10142,22 +10215,22 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>192</v>
+        <v>510</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10182,13 +10255,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10215,7 +10288,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10224,38 +10297,38 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>493</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -10270,16 +10343,16 @@
         <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10304,13 +10377,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10334,10 +10407,10 @@
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10346,31 +10419,31 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10389,19 +10462,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10426,13 +10499,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10450,7 +10523,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10468,31 +10541,29 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10501,31 +10572,31 @@
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10574,7 +10645,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10595,10 +10666,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10607,14 +10678,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10626,25 +10699,29 @@
         <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10692,19 +10769,19 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>83</v>
@@ -10713,10 +10790,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10727,21 +10804,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
@@ -10753,17 +10830,15 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10812,19 +10887,19 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -10836,7 +10911,7 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10847,14 +10922,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10867,26 +10942,24 @@
         <v>83</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O73" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10934,7 +11007,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10958,7 +11031,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10969,45 +11042,45 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>515</v>
+        <v>420</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11032,13 +11105,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11056,34 +11129,34 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11091,10 +11164,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11102,7 +11175,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>94</v>
@@ -11117,19 +11190,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>505</v>
+        <v>192</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11139,7 +11212,7 @@
         <v>83</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>83</v>
+        <v>521</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>83</v>
@@ -11154,13 +11227,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11178,10 +11251,10 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>94</v>
@@ -11199,21 +11272,21 @@
         <v>488</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>489</v>
@@ -11236,22 +11309,22 @@
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>192</v>
+        <v>510</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O76" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11276,13 +11349,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11309,7 +11382,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -11318,38 +11391,38 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>493</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11364,16 +11437,16 @@
         <v>192</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11398,13 +11471,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -11428,10 +11501,10 @@
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11440,31 +11513,31 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11483,19 +11556,19 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11520,13 +11593,13 @@
         <v>83</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -11544,7 +11617,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11562,31 +11635,29 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11595,31 +11666,31 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11668,7 +11739,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11689,10 +11760,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11701,14 +11772,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>83</v>
       </c>
@@ -11720,25 +11793,29 @@
         <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -11786,19 +11863,19 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -11807,10 +11884,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11821,21 +11898,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
@@ -11847,17 +11924,15 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11906,19 +11981,19 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -11930,7 +12005,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11941,14 +12016,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11961,26 +12036,24 @@
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12028,7 +12101,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12052,7 +12125,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12063,45 +12136,45 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>526</v>
+        <v>420</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12126,13 +12199,13 @@
         <v>83</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12150,34 +12223,34 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12185,10 +12258,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12196,7 +12269,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>94</v>
@@ -12211,19 +12284,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>505</v>
+        <v>192</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12233,7 +12306,7 @@
         <v>83</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>83</v>
+        <v>533</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>83</v>
@@ -12248,13 +12321,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12272,10 +12345,10 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>94</v>
@@ -12293,21 +12366,21 @@
         <v>488</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>489</v>
@@ -12330,22 +12403,22 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>192</v>
+        <v>510</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N85" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O85" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12370,13 +12443,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12403,7 +12476,7 @@
         <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>106</v>
@@ -12412,38 +12485,38 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>83</v>
@@ -12458,16 +12531,16 @@
         <v>192</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12492,13 +12565,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12522,10 +12595,10 @@
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -12534,31 +12607,31 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12577,19 +12650,19 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12614,13 +12687,13 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -12638,7 +12711,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12656,31 +12729,29 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>83</v>
       </c>
@@ -12689,31 +12760,31 @@
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12762,7 +12833,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12783,10 +12854,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12795,14 +12866,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>83</v>
       </c>
@@ -12814,25 +12887,29 @@
         <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -12880,19 +12957,19 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
@@ -12901,10 +12978,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12915,21 +12992,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -12941,17 +13018,15 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13000,19 +13075,19 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
@@ -13024,7 +13099,7 @@
         <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13035,14 +13110,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13055,26 +13130,24 @@
         <v>83</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O91" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13122,7 +13195,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13146,7 +13219,7 @@
         <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13157,45 +13230,45 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>537</v>
+        <v>420</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13220,13 +13293,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13244,34 +13317,34 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -13279,10 +13352,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13290,7 +13363,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>94</v>
@@ -13305,19 +13378,19 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13327,7 +13400,7 @@
         <v>83</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>83</v>
@@ -13342,13 +13415,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13366,10 +13439,10 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>94</v>
@@ -13387,21 +13460,21 @@
         <v>488</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>489</v>
@@ -13424,22 +13497,22 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13464,13 +13537,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13497,7 +13570,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -13506,38 +13579,38 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>493</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13552,16 +13625,16 @@
         <v>192</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13586,13 +13659,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13616,10 +13689,10 @@
         <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -13628,31 +13701,31 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13671,19 +13744,19 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13708,13 +13781,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -13732,7 +13805,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13750,31 +13823,29 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13783,31 +13854,31 @@
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13856,7 +13927,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13877,10 +13948,10 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13889,14 +13960,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>83</v>
       </c>
@@ -13908,25 +13981,29 @@
         <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -13974,19 +14051,19 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -13995,10 +14072,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14009,21 +14086,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>83</v>
@@ -14035,17 +14112,15 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14094,19 +14169,19 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>83</v>
@@ -14118,7 +14193,7 @@
         <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14129,14 +14204,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14149,26 +14224,24 @@
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O100" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14216,7 +14289,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14240,7 +14313,7 @@
         <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14251,45 +14324,45 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>548</v>
+        <v>420</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14314,13 +14387,13 @@
         <v>83</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14338,34 +14411,34 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -14373,10 +14446,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14384,7 +14457,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>94</v>
@@ -14399,19 +14472,19 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>505</v>
+        <v>192</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14421,7 +14494,7 @@
         <v>83</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>83</v>
@@ -14436,13 +14509,13 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -14460,10 +14533,10 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>94</v>
@@ -14481,21 +14554,21 @@
         <v>488</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>489</v>
@@ -14518,22 +14591,22 @@
         <v>83</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>192</v>
+        <v>510</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O103" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14558,13 +14631,13 @@
         <v>83</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -14591,7 +14664,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -14600,38 +14673,38 @@
         <v>83</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>493</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>83</v>
@@ -14646,16 +14719,16 @@
         <v>192</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -14680,13 +14753,13 @@
         <v>83</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -14710,10 +14783,10 @@
         <v>81</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -14722,31 +14795,31 @@
         <v>83</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14765,19 +14838,19 @@
         <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -14802,13 +14875,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14826,7 +14899,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14844,31 +14917,29 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>83</v>
       </c>
@@ -14877,31 +14948,31 @@
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -14950,7 +15021,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -14971,10 +15042,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -14983,14 +15054,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="D107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15002,25 +15075,29 @@
         <v>94</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15068,19 +15145,19 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>83</v>
@@ -15089,10 +15166,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15103,21 +15180,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>83</v>
@@ -15129,17 +15206,15 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15188,19 +15263,19 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>83</v>
@@ -15212,7 +15287,7 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15223,14 +15298,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15243,26 +15318,24 @@
         <v>83</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O109" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15310,7 +15383,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15334,7 +15407,7 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15345,45 +15418,45 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J110" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>559</v>
+        <v>420</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15408,13 +15481,13 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -15432,34 +15505,34 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -15467,10 +15540,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15478,7 +15551,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>94</v>
@@ -15493,19 +15566,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>505</v>
+        <v>192</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>487</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15515,7 +15588,7 @@
         <v>83</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>83</v>
+        <v>569</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>83</v>
@@ -15530,13 +15603,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15554,10 +15627,10 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>94</v>
@@ -15575,21 +15648,21 @@
         <v>488</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>489</v>
@@ -15612,22 +15685,22 @@
         <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>192</v>
+        <v>510</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M112" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N112" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O112" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -15652,13 +15725,13 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -15685,7 +15758,7 @@
         <v>94</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>106</v>
@@ -15694,38 +15767,38 @@
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>493</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -15740,16 +15813,16 @@
         <v>192</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -15774,13 +15847,13 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -15804,10 +15877,10 @@
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>106</v>
@@ -15816,31 +15889,31 @@
         <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15859,19 +15932,19 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15896,13 +15969,13 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -15920,7 +15993,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15938,23 +16011,145 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN114" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP114" t="s" s="2">
+      <c r="O115" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP115" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP114">
+  <autoFilter ref="A1:AP115">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15964,7 +16159,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
